--- a/StructureDefinition-open-elis-location.xlsx
+++ b/StructureDefinition-open-elis-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-14T18:31:44+00:00</t>
+    <t>2025-09-03T10:18:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-open-elis-location.xlsx
+++ b/StructureDefinition-open-elis-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-09-03T10:18:48+00:00</t>
+    <t>2026-03-23T16:02:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -340,7 +340,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -661,7 +661,7 @@
     <t>Physical form of the location.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/location-physical-type</t>
+    <t>http://hl7.org/fhir/ValueSet/location-physical-type|4.0.1</t>
   </si>
   <si>
     <t>.playingEntity [classCode=PLC].code</t>
@@ -761,7 +761,7 @@
     <t>Location.managingOrganization</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization)
+    <t xml:space="preserve">Reference(Organization|4.0.1)
 </t>
   </si>
   <si>
@@ -783,7 +783,7 @@
     <t>Location.partOf</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Location)
+    <t xml:space="preserve">Reference(Location|4.0.1)
 </t>
   </si>
   <si>
@@ -886,7 +886,7 @@
     <t>Location.endpoint</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Endpoint)
+    <t xml:space="preserve">Reference(Endpoint|4.0.1)
 </t>
   </si>
   <si>
@@ -1201,7 +1201,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="20.21875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="24.74609375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>

--- a/StructureDefinition-open-elis-location.xlsx
+++ b/StructureDefinition-open-elis-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-23T16:02:58+00:00</t>
+    <t>2026-05-11T11:15:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-open-elis-location.xlsx
+++ b/StructureDefinition-open-elis-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-11T11:15:58+00:00</t>
+    <t>2026-05-11T15:58:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-open-elis-location.xlsx
+++ b/StructureDefinition-open-elis-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-11T15:58:07+00:00</t>
+    <t>2026-05-12T16:33:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
